--- a/data/trans_orig/P64D$andando_2023-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P64D$andando_2023-Clase-trans_orig.xlsx
@@ -504,7 +504,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W46"/>
+  <dimension ref="A1:W40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según cómo se desplaza desde su casa al centro de trabajo/estudios, mediante, al menos, una de las opciones (multirrespuesta) en 2023</t>
+          <t>Población según cómo se desplaza desde su casa al centro de trabajo/estudios, mediante, al menos, una de las opciones (multirrespuesta) en 2023 (tasa de respuesta: 99,46%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>81030</t>
+          <t>81397</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>118055</t>
+          <t>116834</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>23,1%</t>
+          <t>23,2%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>33,65%</t>
+          <t>33,3%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>87155</t>
+          <t>87868</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>114684</t>
+          <t>115298</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>27,88%</t>
+          <t>28,11%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>36,69%</t>
+          <t>36,88%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>176810</t>
+          <t>177238</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>221952</t>
+          <t>223685</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>26,65%</t>
+          <t>26,72%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>33,46%</t>
+          <t>33,72%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>5081</t>
+          <t>5092</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>17622</t>
+          <t>18081</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -863,7 +863,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>5,02%</t>
+          <t>5,15%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -883,7 +883,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>4299</t>
+          <t>5180</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>5973</t>
+          <t>5941</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>19071</t>
+          <t>19680</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -933,7 +933,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>2,97%</t>
         </is>
       </c>
     </row>
@@ -956,12 +956,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>212457</t>
+          <t>212079</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>252430</t>
+          <t>251081</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -971,12 +971,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>60,56%</t>
+          <t>60,46%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>71,96%</t>
+          <t>71,57%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -991,12 +991,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>197346</t>
+          <t>196929</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>226218</t>
+          <t>226929</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1006,12 +1006,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>63,13%</t>
+          <t>63,0%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>72,37%</t>
+          <t>72,6%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1026,12 +1026,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>421833</t>
+          <t>420844</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>468446</t>
+          <t>469031</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1041,12 +1041,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>63,59%</t>
+          <t>63,44%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>70,61%</t>
+          <t>70,7%</t>
         </is>
       </c>
     </row>
@@ -1069,12 +1069,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>14320</t>
+          <t>15633</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>35531</t>
+          <t>36128</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1084,12 +1084,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,08%</t>
+          <t>4,46%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>10,13%</t>
+          <t>10,3%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1104,12 +1104,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>22684</t>
+          <t>22367</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>40415</t>
+          <t>40664</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1119,12 +1119,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>7,26%</t>
+          <t>7,16%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>12,93%</t>
+          <t>13,01%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1139,12 +1139,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>41829</t>
+          <t>41809</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>69180</t>
+          <t>67307</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1154,12 +1154,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>6,31%</t>
+          <t>6,3%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>10,43%</t>
+          <t>10,15%</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1266</t>
+          <t>1212</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>11740</t>
+          <t>11846</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1197,12 +1197,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>3,35%</t>
+          <t>3,38%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1222,7 +1222,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>9003</t>
+          <t>6249</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1237,7 +1237,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1252,12 +1252,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1672</t>
+          <t>1556</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>12684</t>
+          <t>14351</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1267,12 +1267,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>0,23%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>2,16%</t>
         </is>
       </c>
     </row>
@@ -1295,12 +1295,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>16765</t>
+          <t>16230</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>39853</t>
+          <t>38951</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1310,12 +1310,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>4,78%</t>
+          <t>4,63%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>11,36%</t>
+          <t>11,1%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1330,12 +1330,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>8714</t>
+          <t>9104</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>22921</t>
+          <t>23539</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1345,12 +1345,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>2,91%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>7,33%</t>
+          <t>7,53%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1365,12 +1365,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>28753</t>
+          <t>29184</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>54619</t>
+          <t>58118</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1380,12 +1380,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>4,33%</t>
+          <t>4,4%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>8,23%</t>
+          <t>8,76%</t>
         </is>
       </c>
     </row>
@@ -1412,12 +1412,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>49638</t>
+          <t>49451</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>78325</t>
+          <t>78937</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1427,12 +1427,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>16,36%</t>
+          <t>16,3%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>25,82%</t>
+          <t>26,02%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1447,12 +1447,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>67842</t>
+          <t>66110</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>92656</t>
+          <t>92056</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1462,12 +1462,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>26,91%</t>
+          <t>26,22%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>36,75%</t>
+          <t>36,51%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1482,12 +1482,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>123335</t>
+          <t>121251</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>161113</t>
+          <t>161660</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1497,12 +1497,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>22,2%</t>
+          <t>21,83%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>29,0%</t>
+          <t>29,1%</t>
         </is>
       </c>
     </row>
@@ -1525,12 +1525,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1914</t>
+          <t>1907</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>13510</t>
+          <t>15343</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1545,7 +1545,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>4,45%</t>
+          <t>5,06%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1560,12 +1560,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>662</t>
+          <t>666</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>5482</t>
+          <t>5509</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1580,7 +1580,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,18%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1595,12 +1595,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>3314</t>
+          <t>3186</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>15616</t>
+          <t>15692</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1610,12 +1610,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>2,82%</t>
         </is>
       </c>
     </row>
@@ -1638,12 +1638,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>195604</t>
+          <t>195897</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>231117</t>
+          <t>230790</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1653,12 +1653,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>64,48%</t>
+          <t>64,58%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>76,19%</t>
+          <t>76,08%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1673,12 +1673,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>146409</t>
+          <t>146066</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>174137</t>
+          <t>174870</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1688,12 +1688,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>58,07%</t>
+          <t>57,93%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>69,07%</t>
+          <t>69,36%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1708,12 +1708,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>354576</t>
+          <t>354623</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>397676</t>
+          <t>398406</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1723,12 +1723,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>63,83%</t>
+          <t>63,84%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>71,59%</t>
+          <t>71,72%</t>
         </is>
       </c>
     </row>
@@ -1751,12 +1751,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>15406</t>
+          <t>15625</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>34472</t>
+          <t>33981</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1766,12 +1766,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,08%</t>
+          <t>5,15%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>11,36%</t>
+          <t>11,2%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1786,12 +1786,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>18178</t>
+          <t>17917</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>35273</t>
+          <t>34805</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1801,12 +1801,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>7,21%</t>
+          <t>7,11%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>13,99%</t>
+          <t>13,8%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1821,12 +1821,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>38130</t>
+          <t>37232</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>63469</t>
+          <t>62129</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1836,12 +1836,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>6,86%</t>
+          <t>6,7%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>11,43%</t>
+          <t>11,19%</t>
         </is>
       </c>
     </row>
@@ -1869,7 +1869,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>4755</t>
+          <t>4565</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1884,7 +1884,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1904,7 +1904,7 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>7935</t>
+          <t>9650</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1919,7 +1919,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>3,15%</t>
+          <t>3,83%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1934,12 +1934,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>663</t>
+          <t>659</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>8772</t>
+          <t>10177</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1954,7 +1954,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,83%</t>
         </is>
       </c>
     </row>
@@ -1977,12 +1977,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>14434</t>
+          <t>14191</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>44059</t>
+          <t>42040</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1992,12 +1992,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>4,76%</t>
+          <t>4,68%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>14,52%</t>
+          <t>13,86%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2012,12 +2012,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>12701</t>
+          <t>12835</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>29006</t>
+          <t>28162</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2027,12 +2027,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>5,04%</t>
+          <t>5,09%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>11,5%</t>
+          <t>11,17%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2047,12 +2047,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>31193</t>
+          <t>32425</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>59929</t>
+          <t>62342</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>5,62%</t>
+          <t>5,84%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>10,79%</t>
+          <t>11,22%</t>
         </is>
       </c>
     </row>
@@ -2094,12 +2094,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>15962</t>
+          <t>15514</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>124726</t>
+          <t>127395</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2109,12 +2109,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>3,17%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>25,48%</t>
+          <t>26,02%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2129,12 +2129,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>27726</t>
+          <t>27992</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>41571</t>
+          <t>42826</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2144,12 +2144,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>37,87%</t>
+          <t>38,23%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>56,78%</t>
+          <t>58,5%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2164,12 +2164,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>26408</t>
+          <t>36992</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>175418</t>
+          <t>174278</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2179,12 +2179,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>4,69%</t>
+          <t>6,57%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>31,17%</t>
+          <t>30,97%</t>
         </is>
       </c>
     </row>
@@ -2212,7 +2212,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>17809</t>
+          <t>18156</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2227,7 +2227,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>3,71%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2247,7 +2247,7 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>5455</t>
+          <t>4373</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2262,7 +2262,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>7,45%</t>
+          <t>5,97%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2277,12 +2277,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>977</t>
+          <t>1080</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>18331</t>
+          <t>19299</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2292,12 +2292,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>0,17%</t>
+          <t>0,19%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>3,43%</t>
         </is>
       </c>
     </row>
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>369292</t>
+          <t>365429</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>473908</t>
+          <t>476121</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2335,12 +2335,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>75,44%</t>
+          <t>74,65%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>96,81%</t>
+          <t>97,26%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2355,12 +2355,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>29180</t>
+          <t>28824</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>43181</t>
+          <t>44213</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2370,12 +2370,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>39,86%</t>
+          <t>39,37%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>58,98%</t>
+          <t>60,39%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2390,12 +2390,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>388769</t>
+          <t>386524</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>535455</t>
+          <t>525562</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2405,12 +2405,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>69,09%</t>
+          <t>68,69%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>95,15%</t>
+          <t>93,39%</t>
         </is>
       </c>
     </row>
@@ -2433,12 +2433,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>3281</t>
+          <t>2748</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>35096</t>
+          <t>35342</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2448,12 +2448,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>7,17%</t>
+          <t>7,22%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2468,12 +2468,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>586</t>
+          <t>595</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>5253</t>
+          <t>5636</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>7,17%</t>
+          <t>7,7%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2503,12 +2503,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>3562</t>
+          <t>4544</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>35727</t>
+          <t>35628</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>6,35%</t>
+          <t>6,33%</t>
         </is>
       </c>
     </row>
@@ -2551,7 +2551,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>8287</t>
+          <t>8474</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2566,7 +2566,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2581,62 +2581,62 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q20" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R20" s="2" t="inlineStr">
+        <is>
+          <t>1408</t>
+        </is>
+      </c>
+      <c r="S20" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>1190</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
+      <c r="T20" s="2" t="inlineStr">
+        <is>
+          <t>7653</t>
+        </is>
+      </c>
+      <c r="U20" s="2" t="inlineStr">
+        <is>
+          <t>0,25%</t>
+        </is>
+      </c>
+      <c r="V20" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O20" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P20" s="2" t="inlineStr">
-        <is>
-          <t>1,62%</t>
-        </is>
-      </c>
-      <c r="Q20" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R20" s="2" t="inlineStr">
-        <is>
-          <t>1408</t>
-        </is>
-      </c>
-      <c r="S20" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T20" s="2" t="inlineStr">
-        <is>
-          <t>7525</t>
-        </is>
-      </c>
-      <c r="U20" s="2" t="inlineStr">
-        <is>
-          <t>0,25%</t>
-        </is>
-      </c>
-      <c r="V20" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,36%</t>
         </is>
       </c>
     </row>
@@ -2659,12 +2659,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>214</t>
+          <t>676</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>17931</t>
+          <t>18889</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2674,12 +2674,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0,04%</t>
+          <t>0,14%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>3,66%</t>
+          <t>3,86%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2694,12 +2694,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>3537</t>
+          <t>3462</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>11339</t>
+          <t>11224</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2709,12 +2709,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>4,83%</t>
+          <t>4,73%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>15,49%</t>
+          <t>15,33%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2729,12 +2729,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>3947</t>
+          <t>3134</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>27198</t>
+          <t>28948</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2744,12 +2744,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>4,83%</t>
+          <t>5,14%</t>
         </is>
       </c>
     </row>
@@ -2776,12 +2776,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>106209</t>
+          <t>105704</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>152072</t>
+          <t>149850</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2791,12 +2791,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>18,98%</t>
+          <t>18,89%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>27,17%</t>
+          <t>26,77%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2811,12 +2811,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>150378</t>
+          <t>151149</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>186360</t>
+          <t>188077</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>35,26%</t>
+          <t>35,44%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>43,7%</t>
+          <t>44,1%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2846,12 +2846,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>270861</t>
+          <t>270614</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>330532</t>
+          <t>329187</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>27,47%</t>
+          <t>27,44%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>33,52%</t>
+          <t>33,38%</t>
         </is>
       </c>
     </row>
@@ -2889,12 +2889,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>1011</t>
+          <t>835</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>7799</t>
+          <t>8016</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2904,12 +2904,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>0,15%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2924,12 +2924,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>632</t>
+          <t>802</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>6581</t>
+          <t>6684</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>0,15%</t>
+          <t>0,19%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2959,12 +2959,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>2651</t>
+          <t>2562</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>11587</t>
+          <t>10900</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,26%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,11%</t>
         </is>
       </c>
     </row>
@@ -3002,12 +3002,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>413633</t>
+          <t>412760</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>459026</t>
+          <t>457307</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3017,12 +3017,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>73,9%</t>
+          <t>73,74%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>82,01%</t>
+          <t>81,7%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3037,12 +3037,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>239210</t>
+          <t>235996</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>274656</t>
+          <t>275312</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3052,12 +3052,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>56,09%</t>
+          <t>55,34%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>64,4%</t>
+          <t>64,56%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3072,12 +3072,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>659042</t>
+          <t>662612</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>719459</t>
+          <t>722195</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3087,12 +3087,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>66,83%</t>
+          <t>67,19%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>72,96%</t>
+          <t>73,23%</t>
         </is>
       </c>
     </row>
@@ -3115,12 +3115,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>29830</t>
+          <t>29419</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>56931</t>
+          <t>57593</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3130,12 +3130,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>5,33%</t>
+          <t>5,26%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>10,17%</t>
+          <t>10,29%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3150,12 +3150,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>35210</t>
+          <t>35123</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>61341</t>
+          <t>60549</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3165,12 +3165,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>8,26%</t>
+          <t>8,24%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>14,38%</t>
+          <t>14,2%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3185,12 +3185,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>71529</t>
+          <t>71190</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>109613</t>
+          <t>110023</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3200,12 +3200,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>7,25%</t>
+          <t>7,22%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>11,12%</t>
+          <t>11,16%</t>
         </is>
       </c>
     </row>
@@ -3228,12 +3228,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>2203</t>
+          <t>2141</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>12196</t>
+          <t>12300</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3243,12 +3243,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3263,12 +3263,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>1157</t>
+          <t>1209</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>9034</t>
+          <t>9579</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3278,12 +3278,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3298,12 +3298,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>4381</t>
+          <t>4819</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>16272</t>
+          <t>16424</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3313,12 +3313,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,67%</t>
         </is>
       </c>
     </row>
@@ -3341,12 +3341,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>5980</t>
+          <t>5703</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>20843</t>
+          <t>20313</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3356,12 +3356,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>3,72%</t>
+          <t>3,63%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3376,12 +3376,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>4451</t>
+          <t>4248</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>13553</t>
+          <t>13057</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3391,12 +3391,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>3,06%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3411,12 +3411,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>12610</t>
+          <t>12815</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>28686</t>
+          <t>30643</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3426,12 +3426,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>3,11%</t>
         </is>
       </c>
     </row>
@@ -3458,12 +3458,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>21523</t>
+          <t>21257</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>44995</t>
+          <t>46945</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3473,12 +3473,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>8,97%</t>
+          <t>8,86%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>18,75%</t>
+          <t>19,57%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3493,12 +3493,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>59088</t>
+          <t>54962</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>143614</t>
+          <t>143426</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3508,12 +3508,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>15,82%</t>
+          <t>14,72%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>38,46%</t>
+          <t>38,41%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3528,12 +3528,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>93604</t>
+          <t>91144</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>167798</t>
+          <t>166592</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3543,12 +3543,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>15,26%</t>
+          <t>14,86%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>27,36%</t>
+          <t>27,16%</t>
         </is>
       </c>
     </row>
@@ -3571,12 +3571,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>153</t>
+          <t>158</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>1347</t>
+          <t>1398</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3586,12 +3586,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>0,06%</t>
+          <t>0,07%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3606,12 +3606,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>193</t>
+          <t>192</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>218262</t>
+          <t>202038</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3626,7 +3626,7 @@
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>58,45%</t>
+          <t>54,1%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3641,12 +3641,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>566</t>
+          <t>665</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>251143</t>
+          <t>218812</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3656,12 +3656,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>0,09%</t>
+          <t>0,11%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>40,95%</t>
+          <t>35,67%</t>
         </is>
       </c>
     </row>
@@ -3684,12 +3684,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>184974</t>
+          <t>182126</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>209347</t>
+          <t>209731</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3699,12 +3699,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>77,1%</t>
+          <t>75,91%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>87,26%</t>
+          <t>87,42%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3719,12 +3719,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>103367</t>
+          <t>109423</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>254106</t>
+          <t>255024</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3734,12 +3734,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>27,68%</t>
+          <t>29,3%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>68,04%</t>
+          <t>68,29%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3754,12 +3754,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>262835</t>
+          <t>269364</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>456976</t>
+          <t>456985</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3769,12 +3769,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>42,85%</t>
+          <t>43,92%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>74,5%</t>
+          <t>74,51%</t>
         </is>
       </c>
     </row>
@@ -3797,12 +3797,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>13075</t>
+          <t>12589</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>30226</t>
+          <t>31050</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3812,12 +3812,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>5,45%</t>
+          <t>5,25%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>12,6%</t>
+          <t>12,94%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3832,12 +3832,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>23619</t>
+          <t>22102</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>63926</t>
+          <t>64921</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3847,12 +3847,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>6,32%</t>
+          <t>5,92%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>17,12%</t>
+          <t>17,38%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3867,12 +3867,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>41969</t>
+          <t>41341</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>85492</t>
+          <t>84273</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3882,12 +3882,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>6,84%</t>
+          <t>6,74%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>13,94%</t>
+          <t>13,74%</t>
         </is>
       </c>
     </row>
@@ -3910,12 +3910,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>941</t>
+          <t>758</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>11030</t>
+          <t>10593</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3925,12 +3925,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>4,6%</t>
+          <t>4,42%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3950,7 +3950,7 @@
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>4901</t>
+          <t>4580</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3965,7 +3965,7 @@
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3980,12 +3980,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>1717</t>
+          <t>1913</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>13243</t>
+          <t>13914</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3995,12 +3995,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,27%</t>
         </is>
       </c>
     </row>
@@ -4028,7 +4028,7 @@
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>4760</t>
+          <t>4464</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -4043,7 +4043,7 @@
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -4058,12 +4058,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>234</t>
+          <t>259</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>4874</t>
+          <t>4753</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4073,12 +4073,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>0,06%</t>
+          <t>0,07%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4093,12 +4093,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>625</t>
+          <t>478</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>5807</t>
+          <t>5462</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -4108,19 +4108,19 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>0,1%</t>
+          <t>0,08%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>0,89%</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
@@ -4130,107 +4130,107 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>395</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>379431</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>247296</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>446322</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>19,53%</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>12,73%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>22,97%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>761</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>488513</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>408689</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>534341</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>33,98%</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>28,42%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>37,16%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1156</t>
         </is>
       </c>
       <c r="R34" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>867943</t>
         </is>
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>644187</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>963194</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>25,67%</t>
         </is>
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>19,05%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>28,49%</t>
         </is>
       </c>
     </row>
@@ -4243,107 +4243,107 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>28</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>24283</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>14149</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>39074</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>17</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>77326</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>6598</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>296983</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>5,38%</t>
         </is>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>20,65%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>45</t>
         </is>
       </c>
       <c r="R35" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>101609</t>
         </is>
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>28365</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>409881</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>3,01%</t>
         </is>
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>12,12%</t>
         </is>
       </c>
     </row>
@@ -4356,107 +4356,107 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1214</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1514286</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1438787</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1659572</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>77,92%</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>74,04%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>85,4%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1230</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>864805</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>728062</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>924484</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>60,15%</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>50,64%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>64,3%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2444</t>
         </is>
       </c>
       <c r="R36" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2379091</t>
         </is>
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2234122</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2587930</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>70,36%</t>
         </is>
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>66,08%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>76,54%</t>
         </is>
       </c>
     </row>
@@ -4469,107 +4469,107 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>128</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>124055</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>84054</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>154579</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>6,38%</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>4,33%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>7,95%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>205</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>147015</t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>120606</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>172420</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>10,22%</t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>8,39%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>11,99%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>333</t>
         </is>
       </c>
       <c r="R37" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>271070</t>
         </is>
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>205855</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>312178</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>8,02%</t>
         </is>
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>6,09%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>9,23%</t>
         </is>
       </c>
     </row>
@@ -4582,107 +4582,107 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>18</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>15738</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>7989</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>26911</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>11</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>8471</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3660</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>15887</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>0,25%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>29</t>
         </is>
       </c>
       <c r="R38" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>24209</t>
         </is>
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>15374</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>36340</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>1,07%</t>
         </is>
       </c>
     </row>
@@ -4695,804 +4695,121 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>65</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>70666</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>45657</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>96655</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>3,64%</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>2,35%</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>4,97%</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>81</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>49857</t>
         </is>
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>37781</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>64557</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>3,47%</t>
         </is>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>4,49%</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>146</t>
         </is>
       </c>
       <c r="R39" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>120523</t>
         </is>
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>91765</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>149389</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>3,56%</t>
         </is>
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>2,71%</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>4,42%</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="B40" s="3" t="inlineStr">
-        <is>
-          <t>Andando</t>
-        </is>
-      </c>
-      <c r="C40" s="2" t="inlineStr">
-        <is>
-          <t>395</t>
-        </is>
-      </c>
-      <c r="D40" s="2" t="inlineStr">
-        <is>
-          <t>379431</t>
-        </is>
-      </c>
-      <c r="E40" s="2" t="inlineStr">
-        <is>
-          <t>259911</t>
-        </is>
-      </c>
-      <c r="F40" s="2" t="inlineStr">
-        <is>
-          <t>447460</t>
-        </is>
-      </c>
-      <c r="G40" s="2" t="inlineStr">
-        <is>
-          <t>19,53%</t>
-        </is>
-      </c>
-      <c r="H40" s="2" t="inlineStr">
-        <is>
-          <t>13,37%</t>
-        </is>
-      </c>
-      <c r="I40" s="2" t="inlineStr">
-        <is>
-          <t>23,03%</t>
-        </is>
-      </c>
-      <c r="J40" s="2" t="inlineStr">
-        <is>
-          <t>761</t>
-        </is>
-      </c>
-      <c r="K40" s="2" t="inlineStr">
-        <is>
-          <t>488513</t>
-        </is>
-      </c>
-      <c r="L40" s="2" t="inlineStr">
-        <is>
-          <t>412823</t>
-        </is>
-      </c>
-      <c r="M40" s="2" t="inlineStr">
-        <is>
-          <t>534231</t>
-        </is>
-      </c>
-      <c r="N40" s="2" t="inlineStr">
-        <is>
-          <t>33,98%</t>
-        </is>
-      </c>
-      <c r="O40" s="2" t="inlineStr">
-        <is>
-          <t>28,71%</t>
-        </is>
-      </c>
-      <c r="P40" s="2" t="inlineStr">
-        <is>
-          <t>37,16%</t>
-        </is>
-      </c>
-      <c r="Q40" s="2" t="inlineStr">
-        <is>
-          <t>1156</t>
-        </is>
-      </c>
-      <c r="R40" s="2" t="inlineStr">
-        <is>
-          <t>867943</t>
-        </is>
-      </c>
-      <c r="S40" s="2" t="inlineStr">
-        <is>
-          <t>667343</t>
-        </is>
-      </c>
-      <c r="T40" s="2" t="inlineStr">
-        <is>
-          <t>967434</t>
-        </is>
-      </c>
-      <c r="U40" s="2" t="inlineStr">
-        <is>
-          <t>25,67%</t>
-        </is>
-      </c>
-      <c r="V40" s="2" t="inlineStr">
-        <is>
-          <t>19,74%</t>
-        </is>
-      </c>
-      <c r="W40" s="2" t="inlineStr">
-        <is>
-          <t>28,61%</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="1" t="n"/>
-      <c r="B41" s="3" t="inlineStr">
-        <is>
-          <t>En bicicleta</t>
-        </is>
-      </c>
-      <c r="C41" s="2" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="D41" s="2" t="inlineStr">
-        <is>
-          <t>24283</t>
-        </is>
-      </c>
-      <c r="E41" s="2" t="inlineStr">
-        <is>
-          <t>14301</t>
-        </is>
-      </c>
-      <c r="F41" s="2" t="inlineStr">
-        <is>
-          <t>37304</t>
-        </is>
-      </c>
-      <c r="G41" s="2" t="inlineStr">
-        <is>
-          <t>1,25%</t>
-        </is>
-      </c>
-      <c r="H41" s="2" t="inlineStr">
-        <is>
-          <t>0,74%</t>
-        </is>
-      </c>
-      <c r="I41" s="2" t="inlineStr">
-        <is>
-          <t>1,92%</t>
-        </is>
-      </c>
-      <c r="J41" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="K41" s="2" t="inlineStr">
-        <is>
-          <t>77326</t>
-        </is>
-      </c>
-      <c r="L41" s="2" t="inlineStr">
-        <is>
-          <t>6898</t>
-        </is>
-      </c>
-      <c r="M41" s="2" t="inlineStr">
-        <is>
-          <t>332658</t>
-        </is>
-      </c>
-      <c r="N41" s="2" t="inlineStr">
-        <is>
-          <t>5,38%</t>
-        </is>
-      </c>
-      <c r="O41" s="2" t="inlineStr">
-        <is>
-          <t>0,48%</t>
-        </is>
-      </c>
-      <c r="P41" s="2" t="inlineStr">
-        <is>
-          <t>23,14%</t>
-        </is>
-      </c>
-      <c r="Q41" s="2" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
-      <c r="R41" s="2" t="inlineStr">
-        <is>
-          <t>101609</t>
-        </is>
-      </c>
-      <c r="S41" s="2" t="inlineStr">
-        <is>
-          <t>29252</t>
-        </is>
-      </c>
-      <c r="T41" s="2" t="inlineStr">
-        <is>
-          <t>379682</t>
-        </is>
-      </c>
-      <c r="U41" s="2" t="inlineStr">
-        <is>
-          <t>3,01%</t>
-        </is>
-      </c>
-      <c r="V41" s="2" t="inlineStr">
-        <is>
-          <t>0,87%</t>
-        </is>
-      </c>
-      <c r="W41" s="2" t="inlineStr">
-        <is>
-          <t>11,23%</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="1" t="n"/>
-      <c r="B42" s="3" t="inlineStr">
-        <is>
-          <t>En vehículo particular</t>
-        </is>
-      </c>
-      <c r="C42" s="2" t="inlineStr">
-        <is>
-          <t>1214</t>
-        </is>
-      </c>
-      <c r="D42" s="2" t="inlineStr">
-        <is>
-          <t>1514286</t>
-        </is>
-      </c>
-      <c r="E42" s="2" t="inlineStr">
-        <is>
-          <t>1439863</t>
-        </is>
-      </c>
-      <c r="F42" s="2" t="inlineStr">
-        <is>
-          <t>1665780</t>
-        </is>
-      </c>
-      <c r="G42" s="2" t="inlineStr">
-        <is>
-          <t>77,92%</t>
-        </is>
-      </c>
-      <c r="H42" s="2" t="inlineStr">
-        <is>
-          <t>74,09%</t>
-        </is>
-      </c>
-      <c r="I42" s="2" t="inlineStr">
-        <is>
-          <t>85,72%</t>
-        </is>
-      </c>
-      <c r="J42" s="2" t="inlineStr">
-        <is>
-          <t>1230</t>
-        </is>
-      </c>
-      <c r="K42" s="2" t="inlineStr">
-        <is>
-          <t>864805</t>
-        </is>
-      </c>
-      <c r="L42" s="2" t="inlineStr">
-        <is>
-          <t>717699</t>
-        </is>
-      </c>
-      <c r="M42" s="2" t="inlineStr">
-        <is>
-          <t>925923</t>
-        </is>
-      </c>
-      <c r="N42" s="2" t="inlineStr">
-        <is>
-          <t>60,15%</t>
-        </is>
-      </c>
-      <c r="O42" s="2" t="inlineStr">
-        <is>
-          <t>49,92%</t>
-        </is>
-      </c>
-      <c r="P42" s="2" t="inlineStr">
-        <is>
-          <t>64,4%</t>
-        </is>
-      </c>
-      <c r="Q42" s="2" t="inlineStr">
-        <is>
-          <t>2444</t>
-        </is>
-      </c>
-      <c r="R42" s="2" t="inlineStr">
-        <is>
-          <t>2379091</t>
-        </is>
-      </c>
-      <c r="S42" s="2" t="inlineStr">
-        <is>
-          <t>2234171</t>
-        </is>
-      </c>
-      <c r="T42" s="2" t="inlineStr">
-        <is>
-          <t>2591024</t>
-        </is>
-      </c>
-      <c r="U42" s="2" t="inlineStr">
-        <is>
-          <t>70,36%</t>
-        </is>
-      </c>
-      <c r="V42" s="2" t="inlineStr">
-        <is>
-          <t>66,08%</t>
-        </is>
-      </c>
-      <c r="W42" s="2" t="inlineStr">
-        <is>
-          <t>76,63%</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="1" t="n"/>
-      <c r="B43" s="3" t="inlineStr">
-        <is>
-          <t>En transporte público</t>
-        </is>
-      </c>
-      <c r="C43" s="2" t="inlineStr">
-        <is>
-          <t>128</t>
-        </is>
-      </c>
-      <c r="D43" s="2" t="inlineStr">
-        <is>
-          <t>124055</t>
-        </is>
-      </c>
-      <c r="E43" s="2" t="inlineStr">
-        <is>
-          <t>82818</t>
-        </is>
-      </c>
-      <c r="F43" s="2" t="inlineStr">
-        <is>
-          <t>153698</t>
-        </is>
-      </c>
-      <c r="G43" s="2" t="inlineStr">
-        <is>
-          <t>6,38%</t>
-        </is>
-      </c>
-      <c r="H43" s="2" t="inlineStr">
-        <is>
-          <t>4,26%</t>
-        </is>
-      </c>
-      <c r="I43" s="2" t="inlineStr">
-        <is>
-          <t>7,91%</t>
-        </is>
-      </c>
-      <c r="J43" s="2" t="inlineStr">
-        <is>
-          <t>205</t>
-        </is>
-      </c>
-      <c r="K43" s="2" t="inlineStr">
-        <is>
-          <t>147015</t>
-        </is>
-      </c>
-      <c r="L43" s="2" t="inlineStr">
-        <is>
-          <t>120307</t>
-        </is>
-      </c>
-      <c r="M43" s="2" t="inlineStr">
-        <is>
-          <t>172459</t>
-        </is>
-      </c>
-      <c r="N43" s="2" t="inlineStr">
-        <is>
-          <t>10,22%</t>
-        </is>
-      </c>
-      <c r="O43" s="2" t="inlineStr">
-        <is>
-          <t>8,37%</t>
-        </is>
-      </c>
-      <c r="P43" s="2" t="inlineStr">
-        <is>
-          <t>11,99%</t>
-        </is>
-      </c>
-      <c r="Q43" s="2" t="inlineStr">
-        <is>
-          <t>333</t>
-        </is>
-      </c>
-      <c r="R43" s="2" t="inlineStr">
-        <is>
-          <t>271070</t>
-        </is>
-      </c>
-      <c r="S43" s="2" t="inlineStr">
-        <is>
-          <t>207077</t>
-        </is>
-      </c>
-      <c r="T43" s="2" t="inlineStr">
-        <is>
-          <t>314902</t>
-        </is>
-      </c>
-      <c r="U43" s="2" t="inlineStr">
-        <is>
-          <t>8,02%</t>
-        </is>
-      </c>
-      <c r="V43" s="2" t="inlineStr">
-        <is>
-          <t>6,12%</t>
-        </is>
-      </c>
-      <c r="W43" s="2" t="inlineStr">
-        <is>
-          <t>9,31%</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="1" t="n"/>
-      <c r="B44" s="3" t="inlineStr">
-        <is>
-          <t>En otros medios</t>
-        </is>
-      </c>
-      <c r="C44" s="2" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="D44" s="2" t="inlineStr">
-        <is>
-          <t>15738</t>
-        </is>
-      </c>
-      <c r="E44" s="2" t="inlineStr">
-        <is>
-          <t>8412</t>
-        </is>
-      </c>
-      <c r="F44" s="2" t="inlineStr">
-        <is>
-          <t>26116</t>
-        </is>
-      </c>
-      <c r="G44" s="2" t="inlineStr">
-        <is>
-          <t>0,81%</t>
-        </is>
-      </c>
-      <c r="H44" s="2" t="inlineStr">
-        <is>
-          <t>0,43%</t>
-        </is>
-      </c>
-      <c r="I44" s="2" t="inlineStr">
-        <is>
-          <t>1,34%</t>
-        </is>
-      </c>
-      <c r="J44" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="K44" s="2" t="inlineStr">
-        <is>
-          <t>8471</t>
-        </is>
-      </c>
-      <c r="L44" s="2" t="inlineStr">
-        <is>
-          <t>3804</t>
-        </is>
-      </c>
-      <c r="M44" s="2" t="inlineStr">
-        <is>
-          <t>16811</t>
-        </is>
-      </c>
-      <c r="N44" s="2" t="inlineStr">
-        <is>
-          <t>0,59%</t>
-        </is>
-      </c>
-      <c r="O44" s="2" t="inlineStr">
-        <is>
-          <t>0,26%</t>
-        </is>
-      </c>
-      <c r="P44" s="2" t="inlineStr">
-        <is>
-          <t>1,17%</t>
-        </is>
-      </c>
-      <c r="Q44" s="2" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
-      <c r="R44" s="2" t="inlineStr">
-        <is>
-          <t>24209</t>
-        </is>
-      </c>
-      <c r="S44" s="2" t="inlineStr">
-        <is>
-          <t>15481</t>
-        </is>
-      </c>
-      <c r="T44" s="2" t="inlineStr">
-        <is>
-          <t>36176</t>
-        </is>
-      </c>
-      <c r="U44" s="2" t="inlineStr">
-        <is>
-          <t>0,72%</t>
-        </is>
-      </c>
-      <c r="V44" s="2" t="inlineStr">
-        <is>
-          <t>0,46%</t>
-        </is>
-      </c>
-      <c r="W44" s="2" t="inlineStr">
-        <is>
-          <t>1,07%</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="1" t="n"/>
-      <c r="B45" s="3" t="inlineStr">
-        <is>
-          <t>No realiza estos trayectos</t>
-        </is>
-      </c>
-      <c r="C45" s="2" t="inlineStr">
-        <is>
-          <t>65</t>
-        </is>
-      </c>
-      <c r="D45" s="2" t="inlineStr">
-        <is>
-          <t>70666</t>
-        </is>
-      </c>
-      <c r="E45" s="2" t="inlineStr">
-        <is>
-          <t>44818</t>
-        </is>
-      </c>
-      <c r="F45" s="2" t="inlineStr">
-        <is>
-          <t>93349</t>
-        </is>
-      </c>
-      <c r="G45" s="2" t="inlineStr">
-        <is>
-          <t>3,64%</t>
-        </is>
-      </c>
-      <c r="H45" s="2" t="inlineStr">
-        <is>
-          <t>2,31%</t>
-        </is>
-      </c>
-      <c r="I45" s="2" t="inlineStr">
-        <is>
-          <t>4,8%</t>
-        </is>
-      </c>
-      <c r="J45" s="2" t="inlineStr">
-        <is>
-          <t>81</t>
-        </is>
-      </c>
-      <c r="K45" s="2" t="inlineStr">
-        <is>
-          <t>49857</t>
-        </is>
-      </c>
-      <c r="L45" s="2" t="inlineStr">
-        <is>
-          <t>37620</t>
-        </is>
-      </c>
-      <c r="M45" s="2" t="inlineStr">
-        <is>
-          <t>65761</t>
-        </is>
-      </c>
-      <c r="N45" s="2" t="inlineStr">
-        <is>
-          <t>3,47%</t>
-        </is>
-      </c>
-      <c r="O45" s="2" t="inlineStr">
-        <is>
-          <t>2,62%</t>
-        </is>
-      </c>
-      <c r="P45" s="2" t="inlineStr">
-        <is>
-          <t>4,57%</t>
-        </is>
-      </c>
-      <c r="Q45" s="2" t="inlineStr">
-        <is>
-          <t>146</t>
-        </is>
-      </c>
-      <c r="R45" s="2" t="inlineStr">
-        <is>
-          <t>120523</t>
-        </is>
-      </c>
-      <c r="S45" s="2" t="inlineStr">
-        <is>
-          <t>91969</t>
-        </is>
-      </c>
-      <c r="T45" s="2" t="inlineStr">
-        <is>
-          <t>151077</t>
-        </is>
-      </c>
-      <c r="U45" s="2" t="inlineStr">
-        <is>
-          <t>3,56%</t>
-        </is>
-      </c>
-      <c r="V45" s="2" t="inlineStr">
-        <is>
-          <t>2,72%</t>
-        </is>
-      </c>
-      <c r="W45" s="2" t="inlineStr">
-        <is>
-          <t>4,47%</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
+      <c r="A40" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (adultos)</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="11">
+  <mergeCells count="10">
     <mergeCell ref="J1:P1"/>
     <mergeCell ref="A22:A27"/>
-    <mergeCell ref="A40:A45"/>
     <mergeCell ref="A4:A9"/>
     <mergeCell ref="A16:A21"/>
     <mergeCell ref="A34:A39"/>

--- a/data/trans_orig/P64D$andando_2023-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P64D$andando_2023-Clase-trans_orig.xlsx
@@ -725,32 +725,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>98094</t>
+          <t>104538</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>81397</t>
+          <t>85321</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>116834</t>
+          <t>122908</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>27,96%</t>
+          <t>27,39%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>23,2%</t>
+          <t>22,35%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>33,3%</t>
+          <t>32,2%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,32 +760,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>100783</t>
+          <t>106967</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>87868</t>
+          <t>92220</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>115298</t>
+          <t>121571</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>32,24%</t>
+          <t>32,11%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>28,11%</t>
+          <t>27,69%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>36,88%</t>
+          <t>36,5%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>198877</t>
+          <t>211505</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>177238</t>
+          <t>189255</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>223685</t>
+          <t>237581</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>29,98%</t>
+          <t>29,59%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>26,72%</t>
+          <t>26,48%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>33,72%</t>
+          <t>33,24%</t>
         </is>
       </c>
     </row>
@@ -838,32 +838,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>9993</t>
+          <t>11329</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>5092</t>
+          <t>6080</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>18081</t>
+          <t>19618</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>2,97%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>5,15%</t>
+          <t>5,14%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,7 +873,7 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>1391</t>
+          <t>1459</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
@@ -883,12 +883,12 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>5180</t>
+          <t>5135</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,27 +908,27 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>11384</t>
+          <t>12788</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>5941</t>
+          <t>6934</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>19680</t>
+          <t>21198</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,79%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -951,32 +951,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>232274</t>
+          <t>248780</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>212079</t>
+          <t>228833</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>251081</t>
+          <t>269547</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>66,21%</t>
+          <t>65,18%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>60,46%</t>
+          <t>59,96%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>71,57%</t>
+          <t>70,62%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>212772</t>
+          <t>223864</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>196929</t>
+          <t>208342</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>226929</t>
+          <t>238836</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>68,07%</t>
+          <t>67,21%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>63,0%</t>
+          <t>62,55%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>72,6%</t>
+          <t>71,7%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>445046</t>
+          <t>472644</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>420844</t>
+          <t>443732</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>469031</t>
+          <t>497566</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>67,09%</t>
+          <t>66,13%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>63,44%</t>
+          <t>62,08%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>70,7%</t>
+          <t>69,61%</t>
         </is>
       </c>
     </row>
@@ -1064,32 +1064,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>23758</t>
+          <t>26715</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>15633</t>
+          <t>17892</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>36128</t>
+          <t>41089</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>6,77%</t>
+          <t>7,0%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,46%</t>
+          <t>4,69%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>10,3%</t>
+          <t>10,77%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1099,32 +1099,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>30421</t>
+          <t>33247</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>22367</t>
+          <t>25080</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>40664</t>
+          <t>44294</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>9,73%</t>
+          <t>9,98%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>7,16%</t>
+          <t>7,53%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>13,01%</t>
+          <t>13,3%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1134,32 +1134,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>54180</t>
+          <t>59962</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>41809</t>
+          <t>46612</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>67307</t>
+          <t>75659</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>8,17%</t>
+          <t>8,39%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>6,3%</t>
+          <t>6,52%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>10,15%</t>
+          <t>10,59%</t>
         </is>
       </c>
     </row>
@@ -1177,32 +1177,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>4095</t>
+          <t>5422</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1212</t>
+          <t>1416</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>11846</t>
+          <t>13515</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>3,38%</t>
+          <t>3,54%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1212,7 +1212,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>1541</t>
+          <t>1483</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
@@ -1222,12 +1222,12 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>6249</t>
+          <t>7207</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
@@ -1237,7 +1237,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1247,32 +1247,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>5636</t>
+          <t>6905</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1556</t>
+          <t>2674</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>14351</t>
+          <t>14349</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>0,23%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,01%</t>
         </is>
       </c>
     </row>
@@ -1290,32 +1290,32 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>26659</t>
+          <t>34418</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>16230</t>
+          <t>21378</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>38951</t>
+          <t>48677</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>7,6%</t>
+          <t>9,02%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>4,63%</t>
+          <t>5,6%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>11,1%</t>
+          <t>12,75%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1325,32 +1325,32 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>14560</t>
+          <t>18027</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>9104</t>
+          <t>11506</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>23539</t>
+          <t>26544</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>4,66%</t>
+          <t>5,41%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>3,45%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>7,53%</t>
+          <t>7,97%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1360,32 +1360,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>41219</t>
+          <t>52444</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>29184</t>
+          <t>39153</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>58118</t>
+          <t>71961</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>6,21%</t>
+          <t>7,34%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>5,48%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>8,76%</t>
+          <t>10,07%</t>
         </is>
       </c>
     </row>
@@ -1407,32 +1407,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>62053</t>
+          <t>67214</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>49451</t>
+          <t>53888</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>78937</t>
+          <t>83072</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>20,46%</t>
+          <t>20,95%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>16,3%</t>
+          <t>16,8%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>26,02%</t>
+          <t>25,89%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1442,32 +1442,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>79107</t>
+          <t>85848</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>66110</t>
+          <t>71756</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>92056</t>
+          <t>100020</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>31,38%</t>
+          <t>31,39%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>26,22%</t>
+          <t>26,24%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>36,51%</t>
+          <t>36,57%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1477,32 +1477,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>141160</t>
+          <t>153062</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>121251</t>
+          <t>133557</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>161660</t>
+          <t>173726</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>25,41%</t>
+          <t>25,75%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>21,83%</t>
+          <t>22,47%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>29,1%</t>
+          <t>29,23%</t>
         </is>
       </c>
     </row>
@@ -1520,32 +1520,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>5143</t>
+          <t>5408</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1907</t>
+          <t>1860</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>15343</t>
+          <t>14952</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>5,06%</t>
+          <t>4,66%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1555,32 +1555,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>2048</t>
+          <t>4778</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>666</t>
+          <t>2045</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>5509</t>
+          <t>11169</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>4,08%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1590,32 +1590,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>7190</t>
+          <t>10186</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>3186</t>
+          <t>5157</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>15692</t>
+          <t>20096</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>3,38%</t>
         </is>
       </c>
     </row>
@@ -1633,32 +1633,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>215695</t>
+          <t>229895</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>195897</t>
+          <t>211093</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>230790</t>
+          <t>246597</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>71,11%</t>
+          <t>71,66%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>64,58%</t>
+          <t>65,8%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>76,08%</t>
+          <t>76,86%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1668,32 +1668,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>160403</t>
+          <t>172367</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>146066</t>
+          <t>157444</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>174870</t>
+          <t>186570</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>63,62%</t>
+          <t>63,03%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>57,93%</t>
+          <t>57,57%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>69,36%</t>
+          <t>68,22%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1703,32 +1703,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>376098</t>
+          <t>402262</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>354623</t>
+          <t>380529</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>398406</t>
+          <t>427190</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>67,71%</t>
+          <t>67,69%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>63,84%</t>
+          <t>64,03%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>71,72%</t>
+          <t>71,88%</t>
         </is>
       </c>
     </row>
@@ -1746,32 +1746,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>23515</t>
+          <t>26637</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>15625</t>
+          <t>17116</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>33981</t>
+          <t>38208</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>7,75%</t>
+          <t>8,3%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,15%</t>
+          <t>5,33%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>11,2%</t>
+          <t>11,91%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1781,32 +1781,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>25779</t>
+          <t>28017</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>17917</t>
+          <t>19822</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>34805</t>
+          <t>39509</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>10,22%</t>
+          <t>10,24%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>7,11%</t>
+          <t>7,25%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>13,8%</t>
+          <t>14,45%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1816,32 +1816,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>49294</t>
+          <t>54654</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>37232</t>
+          <t>42759</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>62129</t>
+          <t>69872</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>8,87%</t>
+          <t>9,2%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>6,7%</t>
+          <t>7,19%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>11,19%</t>
+          <t>11,76%</t>
         </is>
       </c>
     </row>
@@ -1859,7 +1859,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>892</t>
+          <t>866</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -1869,12 +1869,12 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>4565</t>
+          <t>4984</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,27%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
@@ -1884,7 +1884,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>2140</t>
+          <t>2150</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
@@ -1904,12 +1904,12 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>9650</t>
+          <t>8016</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
@@ -1919,7 +1919,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>3,83%</t>
+          <t>2,93%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1929,22 +1929,22 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>3032</t>
+          <t>3017</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>659</t>
+          <t>705</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>10177</t>
+          <t>9455</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
@@ -1954,7 +1954,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,59%</t>
         </is>
       </c>
     </row>
@@ -1972,32 +1972,32 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>24147</t>
+          <t>24245</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>14191</t>
+          <t>14653</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>42040</t>
+          <t>39029</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>7,96%</t>
+          <t>7,56%</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>4,68%</t>
+          <t>4,57%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>13,86%</t>
+          <t>12,17%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2007,32 +2007,32 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>19413</t>
+          <t>20964</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>12835</t>
+          <t>14049</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>28162</t>
+          <t>31833</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>7,7%</t>
+          <t>7,67%</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>5,09%</t>
+          <t>5,14%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>11,17%</t>
+          <t>11,64%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2042,32 +2042,32 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>43560</t>
+          <t>45209</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>32425</t>
+          <t>33578</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>62342</t>
+          <t>62422</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
         <is>
-          <t>7,84%</t>
+          <t>7,61%</t>
         </is>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>5,84%</t>
+          <t>5,65%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>11,22%</t>
+          <t>10,5%</t>
         </is>
       </c>
     </row>
@@ -2089,32 +2089,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>59183</t>
+          <t>67339</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>15514</t>
+          <t>53178</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>127395</t>
+          <t>84045</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>12,09%</t>
+          <t>24,81%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>19,59%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>26,02%</t>
+          <t>30,97%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2124,32 +2124,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>34926</t>
+          <t>39148</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>27992</t>
+          <t>31258</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>42826</t>
+          <t>47776</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>47,7%</t>
+          <t>47,18%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>38,23%</t>
+          <t>37,67%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>58,5%</t>
+          <t>57,58%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2159,32 +2159,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>94109</t>
+          <t>106487</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>36992</t>
+          <t>88518</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>174278</t>
+          <t>123223</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>16,72%</t>
+          <t>30,05%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>6,57%</t>
+          <t>24,98%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>30,97%</t>
+          <t>34,77%</t>
         </is>
       </c>
     </row>
@@ -2202,67 +2202,67 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>5432</t>
+          <t>5693</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
+          <t>1208</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>15227</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>2,1%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>0,45%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>5,61%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>1400</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>18156</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>1,11%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>4253</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>1,69%</t>
+        </is>
+      </c>
+      <c r="O17" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>3,71%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>1444</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>4373</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>1,97%</t>
-        </is>
-      </c>
-      <c r="O17" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>5,97%</t>
+          <t>5,13%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2272,32 +2272,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>6876</t>
+          <t>7093</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1080</t>
+          <t>2641</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>19299</t>
+          <t>16654</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>4,7%</t>
         </is>
       </c>
     </row>
@@ -2315,32 +2315,32 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>432279</t>
+          <t>204168</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>365429</t>
+          <t>187807</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>476121</t>
+          <t>219193</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>88,31%</t>
+          <t>75,23%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>74,65%</t>
+          <t>69,2%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>97,26%</t>
+          <t>80,76%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2350,32 +2350,32 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>36309</t>
+          <t>40910</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>28824</t>
+          <t>32725</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>44213</t>
+          <t>48195</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>49,59%</t>
+          <t>49,31%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>39,37%</t>
+          <t>39,44%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>60,39%</t>
+          <t>58,09%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2385,32 +2385,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>468588</t>
+          <t>245078</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>386524</t>
+          <t>227028</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>525562</t>
+          <t>262729</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>83,27%</t>
+          <t>69,16%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>68,69%</t>
+          <t>64,06%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>93,39%</t>
+          <t>74,14%</t>
         </is>
       </c>
     </row>
@@ -2428,32 +2428,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>14585</t>
+          <t>18597</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>2748</t>
+          <t>10308</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>35342</t>
+          <t>30033</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>6,85%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>7,22%</t>
+          <t>11,07%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2463,32 +2463,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>1881</t>
+          <t>2083</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>595</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>5636</t>
+          <t>5612</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,51%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>7,7%</t>
+          <t>6,76%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2498,32 +2498,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>16466</t>
+          <t>20680</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>4544</t>
+          <t>12434</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>35628</t>
+          <t>34610</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>5,84%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>3,51%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>6,33%</t>
+          <t>9,77%</t>
         </is>
       </c>
     </row>
@@ -2541,7 +2541,7 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>1408</t>
+          <t>1271</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -2551,12 +2551,12 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>8474</t>
+          <t>6821</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
@@ -2566,7 +2566,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>2,51%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2611,7 +2611,7 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>1408</t>
+          <t>1271</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
@@ -2621,12 +2621,12 @@
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>7653</t>
+          <t>6415</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
@@ -2636,7 +2636,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,81%</t>
         </is>
       </c>
     </row>
@@ -2654,32 +2654,32 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>7179</t>
+          <t>7900</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>676</t>
+          <t>3404</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>18889</t>
+          <t>16025</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>2,91%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0,14%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>3,86%</t>
+          <t>5,9%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2689,32 +2689,32 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>6675</t>
+          <t>8256</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>3462</t>
+          <t>4551</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>11224</t>
+          <t>14470</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>9,12%</t>
+          <t>9,95%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>4,73%</t>
+          <t>5,49%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>15,33%</t>
+          <t>17,44%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2724,32 +2724,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>13854</t>
+          <t>16156</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>3134</t>
+          <t>9565</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>28948</t>
+          <t>25056</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>4,56%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>5,14%</t>
+          <t>7,07%</t>
         </is>
       </c>
     </row>
@@ -2771,32 +2771,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>128522</t>
+          <t>150954</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>105704</t>
+          <t>127166</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>149850</t>
+          <t>174453</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>22,96%</t>
+          <t>24,32%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>18,89%</t>
+          <t>20,49%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>26,77%</t>
+          <t>28,1%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2806,32 +2806,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>169099</t>
+          <t>192188</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>151149</t>
+          <t>174463</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>188077</t>
+          <t>213020</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>39,65%</t>
+          <t>40,16%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>35,44%</t>
+          <t>36,45%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>44,1%</t>
+          <t>44,51%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2841,32 +2841,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>297621</t>
+          <t>343141</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>270614</t>
+          <t>313000</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>329187</t>
+          <t>375099</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>30,18%</t>
+          <t>31,21%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>27,44%</t>
+          <t>28,47%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>33,38%</t>
+          <t>34,12%</t>
         </is>
       </c>
     </row>
@@ -2884,32 +2884,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>3212</t>
+          <t>6487</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>835</t>
+          <t>2262</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>8016</t>
+          <t>13713</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>0,15%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>2,21%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2919,67 +2919,67 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>2500</t>
+          <t>3241</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>802</t>
+          <t>873</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>6684</t>
+          <t>8562</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>0,18%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
+          <t>1,79%</t>
+        </is>
+      </c>
+      <c r="Q23" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="R23" s="2" t="inlineStr">
+        <is>
+          <t>9728</t>
+        </is>
+      </c>
+      <c r="S23" s="2" t="inlineStr">
+        <is>
+          <t>4757</t>
+        </is>
+      </c>
+      <c r="T23" s="2" t="inlineStr">
+        <is>
+          <t>17277</t>
+        </is>
+      </c>
+      <c r="U23" s="2" t="inlineStr">
+        <is>
+          <t>0,88%</t>
+        </is>
+      </c>
+      <c r="V23" s="2" t="inlineStr">
+        <is>
+          <t>0,43%</t>
+        </is>
+      </c>
+      <c r="W23" s="2" t="inlineStr">
+        <is>
           <t>1,57%</t>
-        </is>
-      </c>
-      <c r="Q23" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="R23" s="2" t="inlineStr">
-        <is>
-          <t>5712</t>
-        </is>
-      </c>
-      <c r="S23" s="2" t="inlineStr">
-        <is>
-          <t>2562</t>
-        </is>
-      </c>
-      <c r="T23" s="2" t="inlineStr">
-        <is>
-          <t>10900</t>
-        </is>
-      </c>
-      <c r="U23" s="2" t="inlineStr">
-        <is>
-          <t>0,58%</t>
-        </is>
-      </c>
-      <c r="V23" s="2" t="inlineStr">
-        <is>
-          <t>0,26%</t>
-        </is>
-      </c>
-      <c r="W23" s="2" t="inlineStr">
-        <is>
-          <t>1,11%</t>
         </is>
       </c>
     </row>
@@ -2997,32 +2997,32 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>435929</t>
+          <t>463591</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>412760</t>
+          <t>437952</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>457307</t>
+          <t>487278</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>77,88%</t>
+          <t>74,68%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>73,74%</t>
+          <t>70,55%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>81,7%</t>
+          <t>78,5%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3032,32 +3032,32 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>256929</t>
+          <t>277583</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>235996</t>
+          <t>258695</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>275312</t>
+          <t>299047</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>60,25%</t>
+          <t>58,0%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>55,34%</t>
+          <t>54,05%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>64,56%</t>
+          <t>62,48%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3067,32 +3067,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>692858</t>
+          <t>741174</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>662612</t>
+          <t>710164</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>722195</t>
+          <t>773939</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>70,26%</t>
+          <t>67,42%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>67,19%</t>
+          <t>64,6%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>73,23%</t>
+          <t>70,4%</t>
         </is>
       </c>
     </row>
@@ -3110,32 +3110,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>42078</t>
+          <t>53374</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>29419</t>
+          <t>38893</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>57593</t>
+          <t>72809</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>7,52%</t>
+          <t>8,6%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>5,26%</t>
+          <t>6,27%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>10,29%</t>
+          <t>11,73%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3145,32 +3145,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>46411</t>
+          <t>55985</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>35123</t>
+          <t>42231</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>60549</t>
+          <t>71454</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>10,88%</t>
+          <t>11,7%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>8,24%</t>
+          <t>8,82%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>14,2%</t>
+          <t>14,93%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3180,32 +3180,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>88489</t>
+          <t>109359</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>71190</t>
+          <t>91259</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>110023</t>
+          <t>131229</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>8,97%</t>
+          <t>9,95%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>7,22%</t>
+          <t>8,3%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>11,16%</t>
+          <t>11,94%</t>
         </is>
       </c>
     </row>
@@ -3223,32 +3223,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>5536</t>
+          <t>8254</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>2141</t>
+          <t>3613</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>12300</t>
+          <t>16578</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,67%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3258,32 +3258,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>3465</t>
+          <t>7276</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>1209</t>
+          <t>2622</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>9579</t>
+          <t>16027</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>3,35%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3293,32 +3293,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>9001</t>
+          <t>15529</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>4819</t>
+          <t>8745</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>16424</t>
+          <t>27189</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>2,47%</t>
         </is>
       </c>
     </row>
@@ -3336,32 +3336,32 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>11781</t>
+          <t>13481</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>5703</t>
+          <t>7097</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>20313</t>
+          <t>22967</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,17%</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>3,7%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3371,32 +3371,32 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>8012</t>
+          <t>9909</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>4248</t>
+          <t>5250</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>13057</t>
+          <t>16117</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>3,37%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3406,32 +3406,32 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>19794</t>
+          <t>23391</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>12815</t>
+          <t>15368</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>30643</t>
+          <t>34750</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>2,13%</t>
         </is>
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>3,16%</t>
         </is>
       </c>
     </row>
@@ -3453,32 +3453,32 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>31579</t>
+          <t>44206</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>21257</t>
+          <t>31088</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>46945</t>
+          <t>62170</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>13,16%</t>
+          <t>14,4%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>8,86%</t>
+          <t>10,13%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>19,57%</t>
+          <t>20,26%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3488,32 +3488,32 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>104598</t>
+          <t>118098</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>54962</t>
+          <t>103677</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>143426</t>
+          <t>133935</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>28,01%</t>
+          <t>37,73%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>14,72%</t>
+          <t>33,13%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>38,41%</t>
+          <t>42,79%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3523,32 +3523,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>136176</t>
+          <t>162304</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>91144</t>
+          <t>140214</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>166592</t>
+          <t>186990</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>22,2%</t>
+          <t>26,18%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>14,86%</t>
+          <t>22,62%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>27,16%</t>
+          <t>30,17%</t>
         </is>
       </c>
     </row>
@@ -3566,32 +3566,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>503</t>
+          <t>9011</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>158</t>
+          <t>2177</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>1398</t>
+          <t>27162</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>2,94%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>0,07%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>8,85%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3601,32 +3601,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>69943</t>
+          <t>2382</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>192</t>
+          <t>707</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>202038</t>
+          <t>7219</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>18,73%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>0,05%</t>
+          <t>0,23%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>54,1%</t>
+          <t>2,31%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3636,32 +3636,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>70447</t>
+          <t>11393</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>665</t>
+          <t>3940</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>218812</t>
+          <t>29913</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>11,49%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>0,11%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>35,67%</t>
+          <t>4,83%</t>
         </is>
       </c>
     </row>
@@ -3679,32 +3679,32 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>198109</t>
+          <t>240704</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>182126</t>
+          <t>221989</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>209731</t>
+          <t>256416</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>82,58%</t>
+          <t>78,43%</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>75,91%</t>
+          <t>72,34%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>87,42%</t>
+          <t>83,55%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3714,32 +3714,32 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>198393</t>
+          <t>188139</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>109423</t>
+          <t>172671</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>255024</t>
+          <t>203142</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>53,13%</t>
+          <t>60,11%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>29,3%</t>
+          <t>55,17%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>68,29%</t>
+          <t>64,91%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3749,32 +3749,32 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>396501</t>
+          <t>428844</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>269364</t>
+          <t>404589</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>456985</t>
+          <t>455288</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>64,64%</t>
+          <t>69,18%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>43,92%</t>
+          <t>65,27%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>74,51%</t>
+          <t>73,45%</t>
         </is>
       </c>
     </row>
@@ -3792,32 +3792,32 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>20119</t>
+          <t>28861</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>12589</t>
+          <t>20297</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>31050</t>
+          <t>42132</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>8,39%</t>
+          <t>9,4%</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>5,25%</t>
+          <t>6,61%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>12,94%</t>
+          <t>13,73%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3827,32 +3827,32 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>42523</t>
+          <t>50407</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>22102</t>
+          <t>39521</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>64921</t>
+          <t>61968</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>11,39%</t>
+          <t>16,11%</t>
         </is>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>5,92%</t>
+          <t>12,63%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>17,38%</t>
+          <t>19,8%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3862,32 +3862,32 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>62641</t>
+          <t>79268</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>41341</t>
+          <t>64044</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>84273</t>
+          <t>98371</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
         <is>
-          <t>10,21%</t>
+          <t>12,79%</t>
         </is>
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>6,74%</t>
+          <t>10,33%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>13,74%</t>
+          <t>15,87%</t>
         </is>
       </c>
     </row>
@@ -3905,32 +3905,32 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>3806</t>
+          <t>4636</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>758</t>
+          <t>1408</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>10593</t>
+          <t>11680</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>4,42%</t>
+          <t>3,81%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3940,7 +3940,7 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>1325</t>
+          <t>1340</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
@@ -3950,12 +3950,12 @@
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>4580</t>
+          <t>4133</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
@@ -3965,7 +3965,7 @@
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3975,32 +3975,32 @@
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t>5132</t>
+          <t>5976</t>
         </is>
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>1913</t>
+          <t>2307</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>13914</t>
+          <t>13039</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,1%</t>
         </is>
       </c>
     </row>
@@ -4018,7 +4018,7 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>900</t>
+          <t>2109</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
@@ -4028,12 +4028,12 @@
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>4464</t>
+          <t>7457</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
@@ -4043,7 +4043,7 @@
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>2,43%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -4053,32 +4053,32 @@
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>1197</t>
+          <t>3302</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>259</t>
+          <t>740</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>4753</t>
+          <t>7967</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>0,07%</t>
+          <t>0,24%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4088,32 +4088,32 @@
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>2097</t>
+          <t>5411</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>478</t>
+          <t>2109</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>5462</t>
+          <t>11738</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
         <is>
+          <t>0,87%</t>
+        </is>
+      </c>
+      <c r="V33" s="2" t="inlineStr">
+        <is>
           <t>0,34%</t>
         </is>
       </c>
-      <c r="V33" s="2" t="inlineStr">
-        <is>
-          <t>0,08%</t>
-        </is>
-      </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>1,89%</t>
         </is>
       </c>
     </row>
@@ -4135,32 +4135,32 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>379431</t>
+          <t>434250</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>247296</t>
+          <t>398662</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>446322</t>
+          <t>478018</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>19,53%</t>
+          <t>22,84%</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>12,73%</t>
+          <t>20,97%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>22,97%</t>
+          <t>25,14%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4170,32 +4170,32 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>488513</t>
+          <t>542249</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>408689</t>
+          <t>509690</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>534341</t>
+          <t>575207</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>33,98%</t>
+          <t>36,61%</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>28,42%</t>
+          <t>34,41%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>37,16%</t>
+          <t>38,84%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4205,32 +4205,32 @@
       </c>
       <c r="R34" s="2" t="inlineStr">
         <is>
-          <t>867943</t>
+          <t>976499</t>
         </is>
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>644187</t>
+          <t>926350</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>963194</t>
+          <t>1030733</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
         <is>
-          <t>25,67%</t>
+          <t>28,87%</t>
         </is>
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>19,05%</t>
+          <t>27,39%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>28,49%</t>
+          <t>30,47%</t>
         </is>
       </c>
     </row>
@@ -4248,32 +4248,32 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>24283</t>
+          <t>37928</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>14149</t>
+          <t>25279</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>39074</t>
+          <t>58729</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,99%</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>3,09%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4283,32 +4283,32 @@
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>77326</t>
+          <t>13260</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>6598</t>
+          <t>8015</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>296983</t>
+          <t>21344</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>5,38%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>20,65%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4318,32 +4318,32 @@
       </c>
       <c r="R35" s="2" t="inlineStr">
         <is>
-          <t>101609</t>
+          <t>51189</t>
         </is>
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>28365</t>
+          <t>36478</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>409881</t>
+          <t>71998</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>12,12%</t>
+          <t>2,13%</t>
         </is>
       </c>
     </row>
@@ -4361,32 +4361,32 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>1514286</t>
+          <t>1387139</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>1438787</t>
+          <t>1342682</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>1659572</t>
+          <t>1428342</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>77,92%</t>
+          <t>72,95%</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>74,04%</t>
+          <t>70,61%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>85,4%</t>
+          <t>75,11%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4396,32 +4396,32 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>864805</t>
+          <t>902864</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>728062</t>
+          <t>869836</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>924484</t>
+          <t>937494</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>60,15%</t>
+          <t>60,96%</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>50,64%</t>
+          <t>58,73%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>64,3%</t>
+          <t>63,3%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4431,32 +4431,32 @@
       </c>
       <c r="R36" s="2" t="inlineStr">
         <is>
-          <t>2379091</t>
+          <t>2290002</t>
         </is>
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>2234122</t>
+          <t>2231723</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>2587930</t>
+          <t>2344420</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
         <is>
-          <t>70,36%</t>
+          <t>67,7%</t>
         </is>
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>66,08%</t>
+          <t>65,98%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>76,54%</t>
+          <t>69,31%</t>
         </is>
       </c>
     </row>
@@ -4474,32 +4474,32 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>124055</t>
+          <t>154184</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>84054</t>
+          <t>129663</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>154579</t>
+          <t>178863</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>6,38%</t>
+          <t>8,11%</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>4,33%</t>
+          <t>6,82%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>7,95%</t>
+          <t>9,41%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4509,32 +4509,32 @@
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>147015</t>
+          <t>169739</t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>120606</t>
+          <t>146704</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>172420</t>
+          <t>191700</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>10,22%</t>
+          <t>11,46%</t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>8,39%</t>
+          <t>9,9%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>11,99%</t>
+          <t>12,94%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4544,32 +4544,32 @@
       </c>
       <c r="R37" s="2" t="inlineStr">
         <is>
-          <t>271070</t>
+          <t>323924</t>
         </is>
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>205855</t>
+          <t>291768</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>312178</t>
+          <t>361033</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
         <is>
-          <t>8,02%</t>
+          <t>9,58%</t>
         </is>
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>6,09%</t>
+          <t>8,63%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>9,23%</t>
+          <t>10,67%</t>
         </is>
       </c>
     </row>
@@ -4587,32 +4587,32 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>15738</t>
+          <t>20449</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>7989</t>
+          <t>12268</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>26911</t>
+          <t>31738</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -4622,32 +4622,32 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>8471</t>
+          <t>12248</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>3660</t>
+          <t>6197</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>15887</t>
+          <t>21657</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4657,32 +4657,32 @@
       </c>
       <c r="R38" s="2" t="inlineStr">
         <is>
-          <t>24209</t>
+          <t>32698</t>
         </is>
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>15374</t>
+          <t>21677</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>36340</t>
+          <t>45769</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,35%</t>
         </is>
       </c>
     </row>
@@ -4700,32 +4700,32 @@
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>70666</t>
+          <t>82154</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>45657</t>
+          <t>63672</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>96655</t>
+          <t>105563</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>4,32%</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>3,35%</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>4,97%</t>
+          <t>5,55%</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
@@ -4735,32 +4735,32 @@
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>49857</t>
+          <t>60457</t>
         </is>
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>37781</t>
+          <t>48221</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>64557</t>
+          <t>74898</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>4,08%</t>
         </is>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>3,26%</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>4,49%</t>
+          <t>5,06%</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -4770,32 +4770,32 @@
       </c>
       <c r="R39" s="2" t="inlineStr">
         <is>
-          <t>120523</t>
+          <t>142611</t>
         </is>
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>91765</t>
+          <t>120245</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>149389</t>
+          <t>171595</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
         <is>
-          <t>3,56%</t>
+          <t>4,22%</t>
         </is>
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>3,55%</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>4,42%</t>
+          <t>5,07%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P64D$andando_2023-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P64D$andando_2023-Clase-trans_orig.xlsx
@@ -941,112 +941,112 @@
       <c r="A6" s="1" t="n"/>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>En vehículo particular</t>
+          <t>No realiza estos trayectos</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>225</t>
+          <t>26</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>248780</t>
+          <t>34418</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>228833</t>
+          <t>21378</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>269547</t>
+          <t>48677</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>65,18%</t>
+          <t>9,02%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>59,96%</t>
+          <t>5,6%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>70,62%</t>
+          <t>12,75%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>298</t>
+          <t>23</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>223864</t>
+          <t>18027</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>208342</t>
+          <t>11506</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>238836</t>
+          <t>26544</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>67,21%</t>
+          <t>5,41%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>62,55%</t>
+          <t>3,45%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>71,7%</t>
+          <t>7,97%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
         <is>
-          <t>523</t>
+          <t>49</t>
         </is>
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>472644</t>
+          <t>52444</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>443732</t>
+          <t>39153</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>497566</t>
+          <t>71961</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>66,13%</t>
+          <t>7,34%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>62,08%</t>
+          <t>5,48%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>69,61%</t>
+          <t>10,07%</t>
         </is>
       </c>
     </row>
@@ -1054,112 +1054,112 @@
       <c r="A7" s="1" t="n"/>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>En transporte público</t>
+          <t>En otros medios</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>26715</t>
+          <t>5422</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>17892</t>
+          <t>1416</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>41089</t>
+          <t>13515</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>7,0%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,69%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>10,77%</t>
+          <t>3,54%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>33247</t>
+          <t>1483</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>25080</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>44294</t>
+          <t>7207</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>9,98%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>7,53%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>13,3%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>5</t>
         </is>
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>59962</t>
+          <t>6905</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>46612</t>
+          <t>2674</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>75659</t>
+          <t>14349</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>8,39%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>6,52%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>10,59%</t>
+          <t>2,01%</t>
         </is>
       </c>
     </row>
@@ -1167,112 +1167,112 @@
       <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>En otros medios</t>
+          <t>En vehículo particular</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>225</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>5422</t>
+          <t>248780</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1416</t>
+          <t>228833</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>13515</t>
+          <t>269547</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>65,18%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>59,96%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>70,62%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>298</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>1483</t>
+          <t>223864</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>208342</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>7207</t>
+          <t>238836</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>67,21%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>62,55%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>71,7%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>523</t>
         </is>
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>6905</t>
+          <t>472644</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2674</t>
+          <t>443732</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>14349</t>
+          <t>497566</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>66,13%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>62,08%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>69,61%</t>
         </is>
       </c>
     </row>
@@ -1280,112 +1280,112 @@
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>No realiza estos trayectos</t>
+          <t>En transporte público</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>22</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>34418</t>
+          <t>26715</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>21378</t>
+          <t>17892</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>48677</t>
+          <t>41089</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>9,02%</t>
+          <t>7,0%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>4,69%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>12,75%</t>
+          <t>10,77%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>42</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>18027</t>
+          <t>33247</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>11506</t>
+          <t>25080</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>26544</t>
+          <t>44294</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>5,41%</t>
+          <t>9,98%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>7,53%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>7,97%</t>
+          <t>13,3%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>64</t>
         </is>
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>52444</t>
+          <t>59962</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>39153</t>
+          <t>46612</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>71961</t>
+          <t>75659</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>7,34%</t>
+          <t>8,39%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>5,48%</t>
+          <t>6,52%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>10,07%</t>
+          <t>10,59%</t>
         </is>
       </c>
     </row>
@@ -1623,112 +1623,112 @@
       <c r="A12" s="1" t="n"/>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>En vehículo particular</t>
+          <t>No realiza estos trayectos</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>196</t>
+          <t>18</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>229895</t>
+          <t>24245</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>211093</t>
+          <t>14653</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>246597</t>
+          <t>39029</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>71,66%</t>
+          <t>7,56%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>65,8%</t>
+          <t>4,57%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>76,86%</t>
+          <t>12,17%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>232</t>
+          <t>27</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>172367</t>
+          <t>20964</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>157444</t>
+          <t>14049</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>186570</t>
+          <t>31833</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>63,03%</t>
+          <t>7,67%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>57,57%</t>
+          <t>5,14%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>68,22%</t>
+          <t>11,64%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
         <is>
-          <t>428</t>
+          <t>45</t>
         </is>
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>402262</t>
+          <t>45209</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>380529</t>
+          <t>33578</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>427190</t>
+          <t>62422</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>67,69%</t>
+          <t>7,61%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>64,03%</t>
+          <t>5,65%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>71,88%</t>
+          <t>10,5%</t>
         </is>
       </c>
     </row>
@@ -1736,112 +1736,112 @@
       <c r="A13" s="1" t="n"/>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>En transporte público</t>
+          <t>En otros medios</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>26637</t>
+          <t>866</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>17116</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>38208</t>
+          <t>4984</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>8,3%</t>
+          <t>0,27%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,33%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>11,91%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>28017</t>
+          <t>2150</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>19822</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>39509</t>
+          <t>8016</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>10,24%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>7,25%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>14,45%</t>
+          <t>2,93%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>3</t>
         </is>
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>54654</t>
+          <t>3017</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>42759</t>
+          <t>705</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>69872</t>
+          <t>9455</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>9,2%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>7,19%</t>
+          <t>0,12%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>11,76%</t>
+          <t>1,59%</t>
         </is>
       </c>
     </row>
@@ -1849,112 +1849,112 @@
       <c r="A14" s="1" t="n"/>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>En otros medios</t>
+          <t>En vehículo particular</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>196</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>866</t>
+          <t>229895</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>211093</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>4984</t>
+          <t>246597</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>71,66%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>65,8%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>76,86%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>232</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>2150</t>
+          <t>172367</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>157444</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>8016</t>
+          <t>186570</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>63,03%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>57,57%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>68,22%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>428</t>
         </is>
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>3017</t>
+          <t>402262</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>705</t>
+          <t>380529</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>9455</t>
+          <t>427190</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>67,69%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0,12%</t>
+          <t>64,03%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>71,88%</t>
         </is>
       </c>
     </row>
@@ -1962,112 +1962,112 @@
       <c r="A15" s="1" t="n"/>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>No realiza estos trayectos</t>
+          <t>En transporte público</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>25</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>24245</t>
+          <t>26637</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>14653</t>
+          <t>17116</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>39029</t>
+          <t>38208</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>7,56%</t>
+          <t>8,3%</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>4,57%</t>
+          <t>5,33%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>12,17%</t>
+          <t>11,91%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>34</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>20964</t>
+          <t>28017</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>14049</t>
+          <t>19822</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>31833</t>
+          <t>39509</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>7,67%</t>
+          <t>10,24%</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>5,14%</t>
+          <t>7,25%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>11,64%</t>
+          <t>14,45%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>59</t>
         </is>
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>45209</t>
+          <t>54654</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>33578</t>
+          <t>42759</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>62422</t>
+          <t>69872</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
         <is>
-          <t>7,61%</t>
+          <t>9,2%</t>
         </is>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>5,65%</t>
+          <t>7,19%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>10,5%</t>
+          <t>11,76%</t>
         </is>
       </c>
     </row>
@@ -2305,112 +2305,112 @@
       <c r="A18" s="1" t="n"/>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>En vehículo particular</t>
+          <t>No realiza estos trayectos</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>183</t>
+          <t>7</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>204168</t>
+          <t>7900</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>187807</t>
+          <t>3404</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>219193</t>
+          <t>16025</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>75,23%</t>
+          <t>2,91%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>69,2%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>80,76%</t>
+          <t>5,9%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>12</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>40910</t>
+          <t>8256</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>32725</t>
+          <t>4551</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>48195</t>
+          <t>14470</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>49,31%</t>
+          <t>9,95%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>39,44%</t>
+          <t>5,49%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>58,09%</t>
+          <t>17,44%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
         <is>
-          <t>237</t>
+          <t>19</t>
         </is>
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>245078</t>
+          <t>16156</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>227028</t>
+          <t>9565</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>262729</t>
+          <t>25056</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>69,16%</t>
+          <t>4,56%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>64,06%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>74,14%</t>
+          <t>7,07%</t>
         </is>
       </c>
     </row>
@@ -2418,112 +2418,112 @@
       <c r="A19" s="1" t="n"/>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>En transporte público</t>
+          <t>En otros medios</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>18597</t>
+          <t>1271</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>10308</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>30033</t>
+          <t>6821</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>6,85%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>11,07%</t>
+          <t>2,51%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>2083</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O19" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P19" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R19" s="2" t="inlineStr">
+        <is>
+          <t>1271</t>
+        </is>
+      </c>
+      <c r="S19" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>5612</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
-        <is>
-          <t>2,51%</t>
-        </is>
-      </c>
-      <c r="O19" s="2" t="inlineStr">
+      <c r="T19" s="2" t="inlineStr">
+        <is>
+          <t>6415</t>
+        </is>
+      </c>
+      <c r="U19" s="2" t="inlineStr">
+        <is>
+          <t>0,36%</t>
+        </is>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P19" s="2" t="inlineStr">
-        <is>
-          <t>6,76%</t>
-        </is>
-      </c>
-      <c r="Q19" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="R19" s="2" t="inlineStr">
-        <is>
-          <t>20680</t>
-        </is>
-      </c>
-      <c r="S19" s="2" t="inlineStr">
-        <is>
-          <t>12434</t>
-        </is>
-      </c>
-      <c r="T19" s="2" t="inlineStr">
-        <is>
-          <t>34610</t>
-        </is>
-      </c>
-      <c r="U19" s="2" t="inlineStr">
-        <is>
-          <t>5,84%</t>
-        </is>
-      </c>
-      <c r="V19" s="2" t="inlineStr">
-        <is>
-          <t>3,51%</t>
-        </is>
-      </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>9,77%</t>
+          <t>1,81%</t>
         </is>
       </c>
     </row>
@@ -2531,112 +2531,112 @@
       <c r="A20" s="1" t="n"/>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>En otros medios</t>
+          <t>En vehículo particular</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>183</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>1271</t>
+          <t>204168</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>187807</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>6821</t>
+          <t>219193</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>75,23%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>69,2%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>80,76%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>54</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>40910</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>32725</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>48195</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>49,31%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>39,44%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>58,09%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>237</t>
         </is>
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>1271</t>
+          <t>245078</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>227028</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>6415</t>
+          <t>262729</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>69,16%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>64,06%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>74,14%</t>
         </is>
       </c>
     </row>
@@ -2644,112 +2644,112 @@
       <c r="A21" s="1" t="n"/>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>No realiza estos trayectos</t>
+          <t>En transporte público</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>14</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>7900</t>
+          <t>18597</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>3404</t>
+          <t>10308</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>16025</t>
+          <t>30033</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>6,85%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>5,9%</t>
+          <t>11,07%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>3</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>8256</t>
+          <t>2083</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>4551</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>14470</t>
+          <t>5612</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>9,95%</t>
+          <t>2,51%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>5,49%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>17,44%</t>
+          <t>6,76%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>17</t>
         </is>
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>16156</t>
+          <t>20680</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>9565</t>
+          <t>12434</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>25056</t>
+          <t>34610</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>4,56%</t>
+          <t>5,84%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>3,51%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>7,07%</t>
+          <t>9,77%</t>
         </is>
       </c>
     </row>
@@ -2987,112 +2987,112 @@
       <c r="A24" s="1" t="n"/>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>En vehículo particular</t>
+          <t>No realiza estos trayectos</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>410</t>
+          <t>12</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>463591</t>
+          <t>13481</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>437952</t>
+          <t>7097</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>487278</t>
+          <t>22967</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>74,68%</t>
+          <t>2,17%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>70,55%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>78,5%</t>
+          <t>3,7%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>382</t>
+          <t>15</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>277583</t>
+          <t>9909</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>258695</t>
+          <t>5250</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>299047</t>
+          <t>16117</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>58,0%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>54,05%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>62,48%</t>
+          <t>3,37%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
         <is>
-          <t>792</t>
+          <t>27</t>
         </is>
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>741174</t>
+          <t>23391</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>710164</t>
+          <t>15368</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>773939</t>
+          <t>34750</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>67,42%</t>
+          <t>2,13%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>64,6%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>70,4%</t>
+          <t>3,16%</t>
         </is>
       </c>
     </row>
@@ -3100,112 +3100,112 @@
       <c r="A25" s="1" t="n"/>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>En transporte público</t>
+          <t>En otros medios</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>8</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>53374</t>
+          <t>8254</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>38893</t>
+          <t>3613</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>72809</t>
+          <t>16578</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>8,6%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>6,27%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>11,73%</t>
+          <t>2,67%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>61</t>
+          <t>6</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>55985</t>
+          <t>7276</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>42231</t>
+          <t>2622</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>71454</t>
+          <t>16027</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>11,7%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>8,82%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>14,93%</t>
+          <t>3,35%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
         <is>
-          <t>103</t>
+          <t>14</t>
         </is>
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>109359</t>
+          <t>15529</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>91259</t>
+          <t>8745</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>131229</t>
+          <t>27189</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>9,95%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>8,3%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>11,94%</t>
+          <t>2,47%</t>
         </is>
       </c>
     </row>
@@ -3213,112 +3213,112 @@
       <c r="A26" s="1" t="n"/>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>En otros medios</t>
+          <t>En vehículo particular</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>410</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>8254</t>
+          <t>463591</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3613</t>
+          <t>437952</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>16578</t>
+          <t>487278</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>74,68%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>70,55%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>78,5%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>382</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>7276</t>
+          <t>277583</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>2622</t>
+          <t>258695</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>16027</t>
+          <t>299047</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>58,0%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>54,05%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>3,35%</t>
+          <t>62,48%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>792</t>
         </is>
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>15529</t>
+          <t>741174</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>8745</t>
+          <t>710164</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>27189</t>
+          <t>773939</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>67,42%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>64,6%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>70,4%</t>
         </is>
       </c>
     </row>
@@ -3326,112 +3326,112 @@
       <c r="A27" s="1" t="n"/>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>No realiza estos trayectos</t>
+          <t>En transporte público</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>42</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>13481</t>
+          <t>53374</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>7097</t>
+          <t>38893</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>22967</t>
+          <t>72809</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>8,6%</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>6,27%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>11,73%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>61</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>9909</t>
+          <t>55985</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>5250</t>
+          <t>42231</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>16117</t>
+          <t>71454</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>11,7%</t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>8,82%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>3,37%</t>
+          <t>14,93%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>103</t>
         </is>
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>23391</t>
+          <t>109359</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>15368</t>
+          <t>91259</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>34750</t>
+          <t>131229</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>9,95%</t>
         </is>
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>8,3%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>11,94%</t>
         </is>
       </c>
     </row>
@@ -3669,112 +3669,112 @@
       <c r="A30" s="1" t="n"/>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>En vehículo particular</t>
+          <t>No realiza estos trayectos</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>240704</t>
+          <t>2109</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>221989</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>256416</t>
+          <t>7457</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>78,43%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>72,34%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>83,55%</t>
+          <t>2,43%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>264</t>
+          <t>4</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>188139</t>
+          <t>3302</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>172671</t>
+          <t>740</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>203142</t>
+          <t>7967</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>60,11%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>55,17%</t>
+          <t>0,24%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>64,91%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
         <is>
-          <t>464</t>
+          <t>6</t>
         </is>
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>428844</t>
+          <t>5411</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>404589</t>
+          <t>2109</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>455288</t>
+          <t>11738</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>69,18%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>65,27%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>73,45%</t>
+          <t>1,89%</t>
         </is>
       </c>
     </row>
@@ -3782,112 +3782,112 @@
       <c r="A31" s="1" t="n"/>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>En transporte público</t>
+          <t>En otros medios</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>28861</t>
+          <t>4636</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>20297</t>
+          <t>1408</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>42132</t>
+          <t>11680</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>9,4%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>6,61%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>13,73%</t>
+          <t>3,81%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>50407</t>
+          <t>1340</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>39521</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>61968</t>
+          <t>4133</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>16,11%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>12,63%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>19,8%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>6</t>
         </is>
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>79268</t>
+          <t>5976</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>64044</t>
+          <t>2307</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>98371</t>
+          <t>13039</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
         <is>
-          <t>12,79%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>10,33%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>15,87%</t>
+          <t>2,1%</t>
         </is>
       </c>
     </row>
@@ -3895,112 +3895,112 @@
       <c r="A32" s="1" t="n"/>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>En otros medios</t>
+          <t>En vehículo particular</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>200</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>4636</t>
+          <t>240704</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>1408</t>
+          <t>221989</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>11680</t>
+          <t>256416</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>78,43%</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>72,34%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>3,81%</t>
+          <t>83,55%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>264</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>1340</t>
+          <t>188139</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>172671</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>4133</t>
+          <t>203142</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>60,11%</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>55,17%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>64,91%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>464</t>
         </is>
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t>5976</t>
+          <t>428844</t>
         </is>
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>2307</t>
+          <t>404589</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>13039</t>
+          <t>455288</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>69,18%</t>
         </is>
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>65,27%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>73,45%</t>
         </is>
       </c>
     </row>
@@ -4008,112 +4008,112 @@
       <c r="A33" s="1" t="n"/>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>No realiza estos trayectos</t>
+          <t>En transporte público</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>25</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>2109</t>
+          <t>28861</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>20297</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>7457</t>
+          <t>42132</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>9,4%</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>6,61%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>13,73%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>65</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>3302</t>
+          <t>50407</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>740</t>
+          <t>39521</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>7967</t>
+          <t>61968</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>16,11%</t>
         </is>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>12,63%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>19,8%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>90</t>
         </is>
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>5411</t>
+          <t>79268</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>2109</t>
+          <t>64044</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>11738</t>
+          <t>98371</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>12,79%</t>
         </is>
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>10,33%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>15,87%</t>
         </is>
       </c>
     </row>
@@ -4351,112 +4351,112 @@
       <c r="A36" s="1" t="n"/>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>En vehículo particular</t>
+          <t>No realiza estos trayectos</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>1214</t>
+          <t>65</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>1387139</t>
+          <t>82154</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>1342682</t>
+          <t>63672</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>1428342</t>
+          <t>105563</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>72,95%</t>
+          <t>4,32%</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>70,61%</t>
+          <t>3,35%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>75,11%</t>
+          <t>5,55%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
         <is>
-          <t>1230</t>
+          <t>81</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>902864</t>
+          <t>60457</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>869836</t>
+          <t>48221</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>937494</t>
+          <t>74898</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>60,96%</t>
+          <t>4,08%</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>58,73%</t>
+          <t>3,26%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>63,3%</t>
+          <t>5,06%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
         <is>
-          <t>2444</t>
+          <t>146</t>
         </is>
       </c>
       <c r="R36" s="2" t="inlineStr">
         <is>
-          <t>2290002</t>
+          <t>142611</t>
         </is>
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>2231723</t>
+          <t>120245</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>2344420</t>
+          <t>171595</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
         <is>
-          <t>67,7%</t>
+          <t>4,22%</t>
         </is>
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>65,98%</t>
+          <t>3,55%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>69,31%</t>
+          <t>5,07%</t>
         </is>
       </c>
     </row>
@@ -4464,112 +4464,112 @@
       <c r="A37" s="1" t="n"/>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>En transporte público</t>
+          <t>En otros medios</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>128</t>
+          <t>18</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>154184</t>
+          <t>20449</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>129663</t>
+          <t>12268</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>178863</t>
+          <t>31738</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>8,11%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>6,82%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>9,41%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>205</t>
+          <t>11</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>169739</t>
+          <t>12248</t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>146704</t>
+          <t>6197</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>191700</t>
+          <t>21657</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>11,46%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>9,9%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>12,94%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
         <is>
-          <t>333</t>
+          <t>29</t>
         </is>
       </c>
       <c r="R37" s="2" t="inlineStr">
         <is>
-          <t>323924</t>
+          <t>32698</t>
         </is>
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>291768</t>
+          <t>21677</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>361033</t>
+          <t>45769</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
         <is>
-          <t>9,58%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>8,63%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>10,67%</t>
+          <t>1,35%</t>
         </is>
       </c>
     </row>
@@ -4577,112 +4577,112 @@
       <c r="A38" s="1" t="n"/>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>En otros medios</t>
+          <t>En vehículo particular</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>1214</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>20449</t>
+          <t>1387139</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>12268</t>
+          <t>1342682</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>31738</t>
+          <t>1428342</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>72,95%</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>70,61%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>75,11%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>1230</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>12248</t>
+          <t>902864</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>6197</t>
+          <t>869836</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>21657</t>
+          <t>937494</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>60,96%</t>
         </is>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>58,73%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>63,3%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>2444</t>
         </is>
       </c>
       <c r="R38" s="2" t="inlineStr">
         <is>
-          <t>32698</t>
+          <t>2290002</t>
         </is>
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>21677</t>
+          <t>2231723</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>45769</t>
+          <t>2344420</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>67,7%</t>
         </is>
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>65,98%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>69,31%</t>
         </is>
       </c>
     </row>
@@ -4690,112 +4690,112 @@
       <c r="A39" s="1" t="n"/>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>No realiza estos trayectos</t>
+          <t>En transporte público</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>128</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>82154</t>
+          <t>154184</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>63672</t>
+          <t>129663</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>105563</t>
+          <t>178863</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>4,32%</t>
+          <t>8,11%</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>3,35%</t>
+          <t>6,82%</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>5,55%</t>
+          <t>9,41%</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>205</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>60457</t>
+          <t>169739</t>
         </is>
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>48221</t>
+          <t>146704</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>74898</t>
+          <t>191700</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
         <is>
-          <t>4,08%</t>
+          <t>11,46%</t>
         </is>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>9,9%</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>5,06%</t>
+          <t>12,94%</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
         <is>
-          <t>146</t>
+          <t>333</t>
         </is>
       </c>
       <c r="R39" s="2" t="inlineStr">
         <is>
-          <t>142611</t>
+          <t>323924</t>
         </is>
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>120245</t>
+          <t>291768</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>171595</t>
+          <t>361033</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
         <is>
-          <t>4,22%</t>
+          <t>9,58%</t>
         </is>
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>8,63%</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>5,07%</t>
+          <t>10,67%</t>
         </is>
       </c>
     </row>
